--- a/cache/open_items_2026-05-18.xlsx
+++ b/cache/open_items_2026-05-18.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="90" customHeight="1">
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2576,39 +2576,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2616,27 +2604,23 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="105" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2646,22 +2630,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2671,12 +2655,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -2686,27 +2670,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="105" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2716,37 +2700,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -2756,27 +2740,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="120" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2786,27 +2770,39 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Low / Required</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2819,18 +2815,22 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+          <t>b0e5ef6a1</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2840,39 +2840,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2880,27 +2868,23 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2915,32 +2899,32 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -2960,7 +2944,7 @@
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2954,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2985,17 +2969,17 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3005,12 +2989,12 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3030,17 +3014,17 @@
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3055,32 +3039,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3090,27 +3074,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="180" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3125,32 +3109,32 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3165,22 +3149,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="180" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3195,32 +3179,32 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3235,22 +3219,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="90" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3260,37 +3244,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3300,27 +3284,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="90" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3330,22 +3314,22 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3355,12 +3339,12 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3375,12 +3359,12 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3374,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3405,32 +3389,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -3445,22 +3429,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="105" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3470,29 +3454,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>shipped (revert candidate)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -3502,27 +3494,27 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="105" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3532,37 +3524,29 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -3572,27 +3556,27 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3602,37 +3586,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -3642,27 +3626,27 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="90" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3672,27 +3656,39 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>in flight</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+        </is>
+      </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3705,18 +3701,22 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56" ht="45" customHeight="1">
+          <t>logs/backtest_750d_quant1_validate2</t>
+        </is>
+      </c>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3726,39 +3726,27 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>High — addresses #1 PF drag</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3771,22 +3759,18 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
-        </is>
-      </c>
-      <c r="N56" s="8" t="inlineStr">
-        <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57" ht="45" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3796,37 +3780,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -3836,17 +3820,17 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3840,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3871,17 +3855,17 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3891,12 +3875,12 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -3911,22 +3895,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="75" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3936,27 +3920,39 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Win: bull-only strategy, period.</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
+        </is>
+      </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3964,65 +3960,57 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="75" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>shipped (diagnosis); pending (fix)</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4030,27 +4018,23 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="105" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -4060,37 +4044,37 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -4100,27 +4084,27 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="105" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -4130,37 +4114,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -4170,7 +4154,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4180,7 +4164,7 @@
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4174,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4205,22 +4189,22 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -4230,7 +4214,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
@@ -4250,7 +4234,7 @@
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4244,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4275,32 +4259,32 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -4320,17 +4304,17 @@
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="60" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -4345,32 +4329,32 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -4390,17 +4374,17 @@
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>PEAD-7</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -4410,27 +4394,39 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>PEAD data pipeline</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Wire EODHD past-earnings surprise + post-report gap</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>1 hr</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Massive time savings</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+        </is>
+      </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4438,23 +4434,27 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>f089b48ef</t>
-        </is>
-      </c>
-      <c r="N66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PEAD-7</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -4464,39 +4464,27 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>PEAD data pipeline</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Wire EODHD past-earnings surprise + post-report gap</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>10 min after answer</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Win: -158 lines + clearer docs.</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
-        </is>
-      </c>
+          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4504,27 +4492,23 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N67" s="8" t="inlineStr">
-        <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="90" customHeight="1">
+          <t>f089b48ef</t>
+        </is>
+      </c>
+      <c r="N67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -4539,32 +4523,32 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
@@ -4584,17 +4568,17 @@
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="90" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -4604,37 +4588,37 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
@@ -4644,17 +4628,17 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4648,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>SCORE-ZERO-LABEL</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -4674,39 +4658,27 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Detail UI / Composite Score</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Score=0 generic SUB-THRESHOLD masked the actual kill cause</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Composite Score gauge always said 'SUB-THRESHOLD · −65 to BUY' for score=0. Now distinguishes PORTFOLIO BRAKE (system-wide pause) vs HARD GATE (per-ticker kill) vs SUPPRESSED vs genuinely SUB-THRESHOLD based on t.decision.reason</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
-        </is>
-      </c>
+          <t>kairos.html — _scoreTierTxt + _scoreDeltaTxt computation rewritten with reason-aware branching</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4714,27 +4686,23 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N70" s="8" t="inlineStr">
-        <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="90" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71" ht="75" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>PREMORTEM-REASON</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -4744,35 +4712,27 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Detail UI / Pre-Mortem</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Pre-Mortem showed boilerplate instead of real kill reason</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>When a ticker is in bundle.killed (e.g., rolling-Sharpe brake or earnings blackout), Pre-Mortem was generating speculative killers from current signals instead of surfacing t.decision.reason. Now prepends real reason with severity tag (PORTFOLIO SAFETY BRAKE / HARD GATE FAIL / SYSTEM KILL)</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
+          <t>kairos.html _qdAutoThesisKillers() — block 0 reads dec.reason and ranks priority 200</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
-        </is>
-      </c>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4780,27 +4740,23 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
-        </is>
-      </c>
-      <c r="N71" s="8" t="inlineStr">
-        <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -4810,33 +4766,37 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
@@ -4846,27 +4806,27 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="135" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -4876,37 +4836,37 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
@@ -4916,27 +4876,27 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="105" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>AIPRED-CORE</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -4946,39 +4906,27 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>ML Edge / AI Prediction</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Workspace AI Prediction sub-tab (23 modules)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Universe-wide forecasting workbench: hero cone · trade-exec strip · live-quote chip · stability badge · stress overlay · landmines · walk-forward equity · cross-horizon coherence · forward distribution histogram · calibration + reliability · universe scans (Top 10 Bulls/Bears/Flip/R:R + SHAP-per-row) · sector rollup · pair trades · open positions overlay · diff vs yesterday · R2000 alpha leak · drift trend · failure log</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
-        </is>
-      </c>
+          <t>kairos.html _qdMlAiBody + 23 sub-modules · shared between Workspaces ML Edge tab and QuantDetail per-ticker view via window._qdMlAiBody</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4986,27 +4934,23 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
-        </is>
-      </c>
-      <c r="N74" s="8" t="inlineStr">
-        <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>AIPRED-AUTOREFRESH</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5016,39 +4960,27 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>ML Edge / Autonomous</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Autonomous launchd jobs (full + intraday refresh)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>5 AM PT full universe + 9/11/13 PT intraday top-100. Loaded + tested 2026-05-18. Output: cache/ml_edge_predictions.json + infra/prototype/ ml_edge_predictions.json</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Win: -50ms FCP.</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
-        </is>
-      </c>
+          <t>infra/launchd/com.swingtrade.ml-edge.plist + .ml-edge-intraday.plist (installed at ~/Library/LaunchAgents/)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr"/>
       <c r="K75" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5056,27 +4988,23 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N75" s="8" t="inlineStr">
-        <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="120" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>AIPRED-SCHWAB</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5086,39 +5014,27 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>ML Edge / Real Quotes</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Real Schwab bid/ask spread overlay (top-100)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Batch-fetches live Schwab quotes for top-100 picks per mode; overrides ADV-band heuristic with real spread_bps; q50_net recomputed; spread_source='schwab_live' stamped</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Win: -100ms FCP.</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
-        </is>
-      </c>
+          <t>ml/run_ml_edge.py post-prediction loop · schwab_client.get_quotes_batch</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr"/>
       <c r="K76" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5126,27 +5042,23 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
-        </is>
-      </c>
-      <c r="N76" s="8" t="inlineStr">
-        <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="135" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>AIPRED-STRESS</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5156,39 +5068,27 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>ML Edge / Stress</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>VIX-regime stress overlay from real historical buckets</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Replaces fixed heuristic shift with bucketed mean from 355K samples (base=355K, spy_down=156K, vix=37K). UI cone label shows 'STRESS · real' vs 'STRESS · heuristic' fallback</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
-        </is>
-      </c>
+          <t>scripts/build_stress_buckets.py · cache/ml/stress_buckets.json · /api/ml-edge-stress-buckets · kairos.html _qdMlAiCone</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
       <c r="K77" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5196,27 +5096,23 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
-        </is>
-      </c>
-      <c r="N77" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>AIPRED-SURVIVORSHIP</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5226,31 +5122,27 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>ML Edge / Survivorship</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Point-in-time R1000/R2000 membership snapshots</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Monthly launchd snapshots S&amp;P/R1000/R2000 to data/membership/*_YYYY-MM.csv. data_fetcher.get_universe_as_of reads them when present. Today's baseline captured 2026-05</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+          <t>scripts/snapshot_membership.py + infra/launchd/com.swingtrade.membership-snapshot.plist + data_fetcher.py</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
-        </is>
-      </c>
+      <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5258,27 +5150,23 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
-        </is>
-      </c>
-      <c r="N78" s="8" t="inlineStr">
-        <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="105" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>AIPRED-TRACK</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5288,39 +5176,27 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>ML Edge / Track Record</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>ML-Edge paper picks history + outcome resolver</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>30 top picks per mode logged to cache/ml_edge_picks_history.jsonl on every run. scripts/resolve_ml_picks.py backfills outcomes via OHLCV lookup. /api/ml-edge-track serves real WR/PF/expectancy</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
-        </is>
-      </c>
+          <t>ml/run_ml_edge.py picks-capture block + scripts/resolve_ml_picks.py + server.py /api/ml-edge-track</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
       <c r="K79" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5328,19 +5204,15 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
-        </is>
-      </c>
-      <c r="N79" s="8" t="inlineStr">
-        <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N79" s="8" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -5348,7 +5220,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>AIPRED-UNIVERSE</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5358,39 +5230,27 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>ML Edge / Universe</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Universe expansion S&amp;P 500 + R1000 + R2000 (2960 tickers)</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>ml/universe_loader.py aggregates EODHD index_components for all 3 indices · --universe flag on run_ml_edge.py · membership flags stamped per-payload · S&amp;P 500=503, R1000=981, R2000=1963, union=2960</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Win: cross-run analytics + audit trail.</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
-        </is>
-      </c>
+          <t>ml/universe_loader.py + ml/run_ml_edge.py + UI universe pills in coverage banner</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
       <c r="K80" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5398,27 +5258,23 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N80" s="8" t="inlineStr">
-        <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="105" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81" ht="90" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -5428,22 +5284,22 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5451,14 +5307,10 @@
           <t>4-6 hrs</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
+      <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -5473,22 +5325,22 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="60" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -5498,37 +5350,33 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
@@ -5538,27 +5386,27 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="120" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="135" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -5568,37 +5416,37 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -5613,22 +5461,22 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="75" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -5638,37 +5486,37 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -5683,22 +5531,22 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="60" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -5708,37 +5556,37 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K85" s="12" t="inlineStr">
@@ -5753,22 +5601,22 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="75" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="120" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -5778,37 +5626,37 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -5818,27 +5666,27 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="90" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="135" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -5848,37 +5696,37 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K87" s="12" t="inlineStr">
@@ -5893,22 +5741,22 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="90" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="75" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -5918,27 +5766,31 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+        </is>
+      </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5951,10 +5803,14 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr"/>
+          <t>94c0c5a01</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="105" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -5962,7 +5818,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -5972,29 +5828,37 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
@@ -6009,22 +5873,22 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N89" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="45" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -6034,37 +5898,37 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
@@ -6079,22 +5943,22 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="90" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="105" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -6104,37 +5968,37 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K91" s="12" t="inlineStr">
@@ -6154,17 +6018,17 @@
       </c>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="75" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6174,27 +6038,39 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="5" t="inlineStr"/>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>shipped (tool); pending (subtype attribution)</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+        </is>
+      </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6202,23 +6078,27 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93" ht="90" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="120" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6228,27 +6108,39 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="5" t="inlineStr"/>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>shipped (DRAFT)</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+        </is>
+      </c>
       <c r="K93" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6256,23 +6148,27 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N93" s="8" t="inlineStr"/>
-    </row>
-    <row r="94" ht="90" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="75" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -6282,27 +6178,39 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+        </is>
+      </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6310,23 +6218,27 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N94" s="8" t="inlineStr"/>
-    </row>
-    <row r="95" ht="75" customHeight="1">
+          <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6336,27 +6248,39 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="5" t="inlineStr"/>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+        </is>
+      </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6364,15 +6288,19 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N95" s="8" t="inlineStr"/>
+          <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="inlineStr">
+        <is>
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="75" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -6380,7 +6308,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -6390,27 +6318,39 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+        </is>
+      </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6418,23 +6358,27 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97" ht="60" customHeight="1">
+          <t>302e9ea00</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="90" customHeight="1">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -6444,37 +6388,37 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K97" s="12" t="inlineStr">
@@ -6484,27 +6428,27 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N97" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="90" customHeight="1">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -6514,39 +6458,27 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="5" t="inlineStr"/>
       <c r="K98" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6554,19 +6486,15 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
-        </is>
-      </c>
-      <c r="N98" s="8" t="inlineStr">
-        <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N98" s="8" t="inlineStr"/>
     </row>
     <row r="99" ht="105" customHeight="1">
       <c r="A99" s="2" t="n">
@@ -6574,7 +6502,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -6584,29 +6512,29 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
         </is>
       </c>
       <c r="K99" s="12" t="inlineStr">
@@ -6621,22 +6549,22 @@
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N99" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="105" customHeight="1">
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="45" customHeight="1">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
@@ -6646,29 +6574,37 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
@@ -6683,22 +6619,22 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N100" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="45" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="90" customHeight="1">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -6708,37 +6644,37 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
@@ -6753,22 +6689,22 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N101" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="45" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="75" customHeight="1">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -6778,34 +6714,26 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
       <c r="K102" s="12" t="inlineStr">
         <is>
@@ -6814,27 +6742,23 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N102" s="8" t="inlineStr">
-        <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="105" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103" ht="90" customHeight="1">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -6844,39 +6768,27 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>1.5 hrs</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="5" t="inlineStr"/>
       <c r="K103" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6884,7 +6796,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
@@ -6892,44 +6804,40 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N103" s="8" t="inlineStr">
-        <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="45" customHeight="1">
+      <c r="N103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104" ht="90" customHeight="1">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -6942,48 +6850,48 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr"/>
     </row>
-    <row r="105" ht="45" customHeight="1">
+    <row r="105" ht="75" customHeight="1">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -6996,48 +6904,48 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N105" s="8" t="inlineStr"/>
     </row>
-    <row r="106" ht="45" customHeight="1">
+    <row r="106" ht="75" customHeight="1">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
-        </is>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-CAP-SWEEP</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -7050,53 +6958,65 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>87336f2de</t>
         </is>
       </c>
       <c r="N106" s="8" t="inlineStr"/>
     </row>
-    <row r="107" ht="45" customHeight="1">
+    <row r="107" ht="60" customHeight="1">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7104,15 +7024,19 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
-        </is>
-      </c>
-      <c r="N107" s="8" t="inlineStr"/>
+          <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N107" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="45" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -7120,37 +7044,49 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr"/>
-      <c r="J108" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Trivial.</t>
+        </is>
+      </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7158,53 +7094,61 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
-        </is>
-      </c>
-      <c r="N108" s="8" t="inlineStr"/>
-    </row>
-    <row r="109" ht="45" customHeight="1">
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N108" s="8" t="inlineStr">
+        <is>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="105" customHeight="1">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-A</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr"/>
-      <c r="J109" s="5" t="inlineStr"/>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+        </is>
+      </c>
       <c r="K109" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7212,53 +7156,61 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
-        </is>
-      </c>
-      <c r="N109" s="8" t="inlineStr"/>
-    </row>
-    <row r="110" ht="45" customHeight="1">
+          <t>9517bbbe9..7229d4ccb</t>
+        </is>
+      </c>
+      <c r="N109" s="8" t="inlineStr">
+        <is>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="105" customHeight="1">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr"/>
-      <c r="J110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+        </is>
+      </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7266,15 +7218,19 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
-        </is>
-      </c>
-      <c r="N110" s="8" t="inlineStr"/>
+          <t>18ef1002e..388c316c4</t>
+        </is>
+      </c>
+      <c r="N110" s="8" t="inlineStr">
+        <is>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="45" customHeight="1">
       <c r="A111" s="2" t="n">
@@ -7282,37 +7238,49 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-2</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr"/>
-      <c r="J111" s="5" t="inlineStr"/>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K111" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7320,15 +7288,19 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
-        </is>
-      </c>
-      <c r="N111" s="8" t="inlineStr"/>
+          <t>5ffdd8e07</t>
+        </is>
+      </c>
+      <c r="N111" s="8" t="inlineStr">
+        <is>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="45" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -7336,36 +7308,44 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RULE-1</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="5" t="inlineStr"/>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
       <c r="J112" s="5" t="inlineStr"/>
       <c r="K112" s="12" t="inlineStr">
         <is>
@@ -7374,53 +7354,69 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
-        </is>
-      </c>
-      <c r="N112" s="8" t="inlineStr"/>
-    </row>
-    <row r="113" ht="45" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N112" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="105" customHeight="1">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K113" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7428,15 +7424,19 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
-        </is>
-      </c>
-      <c r="N113" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N113" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="45" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -7459,17 +7459,17 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N114" s="8" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
@@ -7513,17 +7513,17 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N115" s="8" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -7567,17 +7567,17 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N116" s="8" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
@@ -7621,17 +7621,17 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N117" s="8" t="inlineStr"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
@@ -7675,17 +7675,17 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N118" s="8" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
@@ -7729,17 +7729,17 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N119" s="8" t="inlineStr"/>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -7783,17 +7783,17 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N120" s="8" t="inlineStr"/>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -7924,13 +7924,13 @@
       </c>
       <c r="N122" s="8" t="inlineStr"/>
     </row>
-    <row r="123" ht="60" customHeight="1">
+    <row r="123" ht="45" customHeight="1">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
@@ -7940,34 +7940,26 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr"/>
       <c r="J123" s="5" t="inlineStr"/>
       <c r="K123" s="12" t="inlineStr">
         <is>
@@ -7976,27 +7968,23 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N123" s="8" t="inlineStr">
-        <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="75" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124" ht="45" customHeight="1">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -8006,39 +7994,27 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr"/>
       <c r="K124" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8046,27 +8022,23 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N124" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="75" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N124" s="8" t="inlineStr"/>
+    </row>
+    <row r="125" ht="45" customHeight="1">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -8076,22 +8048,22 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -8104,12 +8076,12 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N125" s="8" t="inlineStr"/>
@@ -8120,7 +8092,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
@@ -8130,34 +8102,26 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr"/>
       <c r="K126" s="12" t="inlineStr">
         <is>
@@ -8166,19 +8130,15 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N126" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N126" s="8" t="inlineStr"/>
     </row>
     <row r="127" ht="45" customHeight="1">
       <c r="A127" s="2" t="n">
@@ -8186,7 +8146,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
@@ -8196,39 +8156,27 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr"/>
       <c r="K127" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8236,27 +8184,23 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
-        </is>
-      </c>
-      <c r="N127" s="8" t="inlineStr">
-        <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="75" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N127" s="8" t="inlineStr"/>
+    </row>
+    <row r="128" ht="45" customHeight="1">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
@@ -8266,39 +8210,27 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+      <c r="J128" s="5" t="inlineStr"/>
       <c r="K128" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8306,27 +8238,23 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N128" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="60" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129" ht="45" customHeight="1">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
@@ -8336,39 +8264,27 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J129" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="5" t="inlineStr"/>
       <c r="K129" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8376,27 +8292,23 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N129" s="8" t="inlineStr">
-        <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="60" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N129" s="8" t="inlineStr"/>
+    </row>
+    <row r="130" ht="45" customHeight="1">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -8406,39 +8318,27 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>2-3 hrs</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Win: safer registry edits + audit trail.</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
-        </is>
-      </c>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8446,27 +8346,23 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N130" s="8" t="inlineStr">
-        <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="60" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131" ht="45" customHeight="1">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -8476,39 +8372,27 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Win: visibility into RBAC changes.</t>
-        </is>
-      </c>
-      <c r="J131" s="5" t="inlineStr">
-        <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
-        </is>
-      </c>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr"/>
       <c r="K131" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8516,27 +8400,23 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N131" s="8" t="inlineStr">
-        <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="60" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N131" s="8" t="inlineStr"/>
+    </row>
+    <row r="132" ht="45" customHeight="1">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -8546,39 +8426,27 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t>Trivial CLI wrapper.</t>
-        </is>
-      </c>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+      <c r="J132" s="5" t="inlineStr"/>
       <c r="K132" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8586,27 +8454,23 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
-        </is>
-      </c>
-      <c r="N132" s="8" t="inlineStr">
-        <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="150" customHeight="1">
+          <t>d0c6c4e04</t>
+        </is>
+      </c>
+      <c r="N132" s="8" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>SETDETAIL-FALLBACK</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -8616,31 +8480,27 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Detail UI / Routing</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>setDetailTicker failed for R2000-only tickers</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Clicking ML Edge picks not in scan bundle (HOOD, ARES, STEM etc.) printed '[kairos] ticker not in scan' and never opened. Now synthesizes minimal t row from window.__mlEdgeCache so detail page opens with _fromMlEdge:true flag</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>kairos.html window.setDetailTicker fallback block</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8648,27 +8508,23 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N133" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="45" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N133" s="8" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
@@ -8678,26 +8534,34 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
       <c r="J134" s="5" t="inlineStr"/>
       <c r="K134" s="12" t="inlineStr">
         <is>
@@ -8706,23 +8570,27 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N134" s="8" t="inlineStr"/>
-    </row>
-    <row r="135" ht="45" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N134" s="8" t="inlineStr">
+        <is>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="75" customHeight="1">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -8732,27 +8600,39 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr"/>
-      <c r="J135" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K135" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8760,23 +8640,27 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N135" s="8" t="inlineStr"/>
-    </row>
-    <row r="136" ht="45" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N135" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="75" customHeight="1">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
@@ -8786,22 +8670,22 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -8814,12 +8698,12 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
+          <t>8b06e56ae</t>
         </is>
       </c>
       <c r="N136" s="8" t="inlineStr"/>
@@ -8830,7 +8714,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
@@ -8840,26 +8724,34 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="12" t="inlineStr">
         <is>
@@ -8868,15 +8760,19 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N137" s="8" t="inlineStr"/>
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N137" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="45" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -8884,7 +8780,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
@@ -8894,27 +8790,39 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8922,23 +8830,27 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N138" s="8" t="inlineStr"/>
-    </row>
-    <row r="139" ht="45" customHeight="1">
+          <t>79fa01a75</t>
+        </is>
+      </c>
+      <c r="N138" s="8" t="inlineStr">
+        <is>
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="75" customHeight="1">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
@@ -8948,27 +8860,39 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr"/>
-      <c r="J139" s="5" t="inlineStr"/>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>User can still bypass with --no-verify in emergencies.</t>
+        </is>
+      </c>
       <c r="K139" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8976,23 +8900,27 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N139" s="8" t="inlineStr"/>
-    </row>
-    <row r="140" ht="45" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N139" s="8" t="inlineStr">
+        <is>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="60" customHeight="1">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
@@ -9002,27 +8930,39 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
-      <c r="J140" s="5" t="inlineStr"/>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+        </is>
+      </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9030,23 +8970,27 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N140" s="8" t="inlineStr">
+        <is>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
@@ -9056,27 +9000,39 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
-      <c r="J141" s="5" t="inlineStr"/>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Win: safer registry edits + audit trail.</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+        </is>
+      </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9084,23 +9040,27 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N141" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
@@ -9110,27 +9070,39 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr"/>
-      <c r="J142" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9138,23 +9110,27 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N142" s="8" t="inlineStr"/>
-    </row>
-    <row r="143" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N142" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
@@ -9164,27 +9140,39 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="5" t="inlineStr"/>
-      <c r="J143" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K143" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9192,23 +9180,27 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N143" s="8" t="inlineStr"/>
-    </row>
-    <row r="144" ht="45" customHeight="1">
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="150" customHeight="1">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
@@ -9218,27 +9210,31 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr"/>
-      <c r="J144" s="5" t="inlineStr"/>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9246,15 +9242,19 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N144" s="8" t="inlineStr"/>
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N144" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="45" customHeight="1">
       <c r="A145" s="2" t="n">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -9310,13 +9310,13 @@
       </c>
       <c r="N145" s="8" t="inlineStr"/>
     </row>
-    <row r="146" ht="120" customHeight="1">
+    <row r="146" ht="45" customHeight="1">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
@@ -9326,39 +9326,27 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J146" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr"/>
+      <c r="J146" s="5" t="inlineStr"/>
       <c r="K146" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9366,27 +9354,23 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N146" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N146" s="8" t="inlineStr"/>
+    </row>
+    <row r="147" ht="45" customHeight="1">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
@@ -9396,22 +9380,22 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -9429,18 +9413,18 @@
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
+          <t>dbbd6b5f6</t>
         </is>
       </c>
       <c r="N147" s="8" t="inlineStr"/>
     </row>
-    <row r="148" ht="105" customHeight="1">
+    <row r="148" ht="45" customHeight="1">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
@@ -9450,31 +9434,27 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr"/>
-      <c r="J148" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J148" s="5" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9482,27 +9462,23 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N148" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="135" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N148" s="8" t="inlineStr"/>
+    </row>
+    <row r="149" ht="45" customHeight="1">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
@@ -9512,39 +9488,27 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
-        </is>
-      </c>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr"/>
+      <c r="J149" s="5" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9552,27 +9516,23 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
-        </is>
-      </c>
-      <c r="N149" s="8" t="inlineStr">
-        <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="120" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N149" s="8" t="inlineStr"/>
+    </row>
+    <row r="150" ht="45" customHeight="1">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
@@ -9582,31 +9542,27 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr"/>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J150" s="5" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9614,19 +9570,15 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N150" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N150" s="8" t="inlineStr"/>
     </row>
     <row r="151" ht="45" customHeight="1">
       <c r="A151" s="2" t="n">
@@ -9634,49 +9586,37 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C151" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-4</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J151" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr"/>
+      <c r="J151" s="5" t="inlineStr"/>
       <c r="K151" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9684,15 +9624,15 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M151" s="3" t="inlineStr"/>
-      <c r="N151" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N151" s="8" t="inlineStr"/>
     </row>
     <row r="152" ht="45" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -9700,49 +9640,37 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C152" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-5</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>verified (no change needed)</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
-      <c r="J152" s="5" t="inlineStr">
-        <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
-        </is>
-      </c>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr"/>
+      <c r="J152" s="5" t="inlineStr"/>
       <c r="K152" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9750,15 +9678,15 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M152" s="3" t="inlineStr"/>
-      <c r="N152" s="8" t="inlineStr">
-        <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N152" s="8" t="inlineStr"/>
     </row>
     <row r="153" ht="45" customHeight="1">
       <c r="A153" s="2" t="n">
@@ -9766,44 +9694,36 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
-        </is>
-      </c>
-      <c r="C153" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-6</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr"/>
       <c r="K153" s="12" t="inlineStr">
         <is>
@@ -9812,19 +9732,15 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
-      <c r="N153" s="8" t="inlineStr">
-        <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
-        </is>
-      </c>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N153" s="8" t="inlineStr"/>
     </row>
     <row r="154" ht="45" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -9832,7 +9748,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
@@ -9842,51 +9758,43 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>5 min after answer</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K154" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="3" t="inlineStr"/>
-      <c r="N154" s="8" t="inlineStr">
-        <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr"/>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N154" s="8" t="inlineStr"/>
     </row>
     <row r="155" ht="45" customHeight="1">
       <c r="A155" s="2" t="n">
@@ -9894,7 +9802,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
@@ -9904,51 +9812,43 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>hours-days each</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
-      <c r="J155" s="5" t="inlineStr">
-        <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K155" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="3" t="inlineStr"/>
-      <c r="N155" s="8" t="inlineStr">
-        <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr"/>
+      <c r="J155" s="5" t="inlineStr"/>
+      <c r="K155" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N155" s="8" t="inlineStr"/>
     </row>
     <row r="156" ht="45" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -9956,114 +9856,106 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>SHARPE-9</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J156" s="5" t="inlineStr">
-        <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K156" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="3" t="inlineStr"/>
-      <c r="N156" s="8" t="inlineStr">
-        <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="75" customHeight="1">
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr"/>
+      <c r="J156" s="5" t="inlineStr"/>
+      <c r="K156" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157" ht="120" customHeight="1">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CONVICTION-TIER-WIRE</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2-4 hrs + backtest validation</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Medium — changes live size or eliminates a layer</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
-        </is>
-      </c>
-      <c r="K157" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
+      <c r="K157" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -10071,142 +9963,898 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="M157" s="3" t="inlineStr"/>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="N157" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="195" customHeight="1">
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="75" customHeight="1">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
+          <t>ENTRY-Q-AB</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Strategy / Gates</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Regime-conditional entry_quality A/B</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr"/>
+      <c r="J158" s="5" t="inlineStr"/>
+      <c r="K158" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>07c3af6a3</t>
+        </is>
+      </c>
+      <c r="N158" s="8" t="inlineStr"/>
+    </row>
+    <row r="159" ht="105" customHeight="1">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>TRACKER-BUY-FILTER</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Tracker/Feedback Loop</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+        </is>
+      </c>
+      <c r="K159" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N159" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="135" customHeight="1">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>Scanner deep refactor</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
+      <c r="K160" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N160" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="120" customHeight="1">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Validation Hygiene</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr"/>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
+      <c r="K161" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N161" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTUM-TAB</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Workspaces / Momentum</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>New 🚀 Momentum workspace tab</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr"/>
+      <c r="J162" s="5" t="inlineStr"/>
+      <c r="K162" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N162" s="8" t="inlineStr"/>
+    </row>
+    <row r="163" ht="45" customHeight="1">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C163" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>Verify backtest persistence (cb1f5a010)</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K163" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr"/>
+      <c r="N163" s="8" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="45" customHeight="1">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>verified (no change needed)</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K164" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr"/>
+      <c r="N164" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="45" customHeight="1">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C165" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>Remove emoji icons from Thesis + Research labels</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr"/>
+      <c r="K165" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
+      <c r="N165" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="45" customHeight="1">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>Code Cleanup (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K166" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="3" t="inlineStr"/>
+      <c r="N166" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="45" customHeight="1">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K167" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="45" customHeight="1">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K168" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="3" t="inlineStr"/>
+      <c r="N168" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="75" customHeight="1">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K169" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr"/>
+      <c r="N169" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="195" customHeight="1">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E170" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
+      <c r="F170" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G158" s="5" t="inlineStr">
+      <c r="G170" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="I170" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J158" s="5" t="inlineStr">
+      <c r="J170" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K158" s="15" t="inlineStr">
+      <c r="K170" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr">
+      <c r="L170" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="M158" s="3" t="inlineStr"/>
-      <c r="N158" s="8" t="inlineStr">
+      <c r="M170" s="3" t="inlineStr"/>
+      <c r="N170" s="8" t="inlineStr">
         <is>
           <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="90" customHeight="1">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
+    <row r="171" ht="90" customHeight="1">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C159" s="13" t="inlineStr">
+      <c r="C171" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>Data / Universe</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E171" s="6" t="inlineStr">
         <is>
           <t>Russell 1000 historical membership (Sharadar SF1)</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
+      <c r="F171" s="5" t="inlineStr">
         <is>
           <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
         </is>
       </c>
-      <c r="G159" s="5" t="inlineStr">
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>$$ + 1 day</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I171" s="5" t="inlineStr">
         <is>
           <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
         </is>
       </c>
-      <c r="J159" s="5" t="inlineStr">
+      <c r="J171" s="5" t="inlineStr">
         <is>
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K159" s="15" t="inlineStr">
+      <c r="K171" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L159" s="2" t="inlineStr">
+      <c r="L171" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="M159" s="3" t="inlineStr"/>
-      <c r="N159" s="8" t="inlineStr">
+      <c r="M171" s="3" t="inlineStr"/>
+      <c r="N171" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -10305,16 +10953,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -10362,16 +11010,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
